--- a/filer/11563392_acharter.xlsx
+++ b/filer/11563392_acharter.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_11563392" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_11563392" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,17 +70,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00444444"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -182,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -242,18 +230,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6976,112 +6952,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="62" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Dansk navn</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>XBRL feltnavn</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2020 t.kr.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2021 t.kr.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2022 t.kr.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2023 t.kr.</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2024 t.kr.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Forklaring</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B3" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WritedownsOfCurrentAssets</t>
-        </is>
-      </c>
-      <c r="C3" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WritedownsOfCurrentAssets</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n"/>
-      <c r="I3" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/filer/11563392_acharter.xlsx
+++ b/filer/11563392_acharter.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-mellem · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/11563392_acharter.xlsx
+++ b/filer/11563392_acharter.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_11563392" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_11563392" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_11563392" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_11563392" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4401,6 +4402,148 @@
       </c>
       <c r="F91" s="13">
         <f>IFERROR($F$32/($F$53+$F$60)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw_11563392'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw_11563392'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw_11563392'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw_11563392'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw_11563392'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw_11563392'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw_11563392'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw_11563392'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw_11563392'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw_11563392'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_11563392'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_11563392'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_11563392'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_11563392'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_11563392'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_11563392'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_11563392'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_11563392'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_11563392'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_11563392'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B98">
+        <f>IF(ABS(('pengestrom_raw_11563392'!$B$2+'pengestrom_raw_11563392'!$B$3+'pengestrom_raw_11563392'!$B$4)-'pengestrom_raw_11563392'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_11563392'!$B$2+'pengestrom_raw_11563392'!$B$3+'pengestrom_raw_11563392'!$B$4)-'pengestrom_raw_11563392'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>IF(ABS(('pengestrom_raw_11563392'!$C$2+'pengestrom_raw_11563392'!$C$3+'pengestrom_raw_11563392'!$C$4)-'pengestrom_raw_11563392'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_11563392'!$C$2+'pengestrom_raw_11563392'!$C$3+'pengestrom_raw_11563392'!$C$4)-'pengestrom_raw_11563392'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>IF(ABS(('pengestrom_raw_11563392'!$D$2+'pengestrom_raw_11563392'!$D$3+'pengestrom_raw_11563392'!$D$4)-'pengestrom_raw_11563392'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_11563392'!$D$2+'pengestrom_raw_11563392'!$D$3+'pengestrom_raw_11563392'!$D$4)-'pengestrom_raw_11563392'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>IF(ABS(('pengestrom_raw_11563392'!$E$2+'pengestrom_raw_11563392'!$E$3+'pengestrom_raw_11563392'!$E$4)-'pengestrom_raw_11563392'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_11563392'!$E$2+'pengestrom_raw_11563392'!$E$3+'pengestrom_raw_11563392'!$E$4)-'pengestrom_raw_11563392'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF(ABS(('pengestrom_raw_11563392'!$F$2+'pengestrom_raw_11563392'!$F$3+'pengestrom_raw_11563392'!$F$4)-'pengestrom_raw_11563392'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_11563392'!$F$2+'pengestrom_raw_11563392'!$F$3+'pengestrom_raw_11563392'!$F$4)-'pengestrom_raw_11563392'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4449,347 +4592,347 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>7896</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>5697</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>9319</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>13089</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>17701</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>3492</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>3846</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>4307</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>4456</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>5304</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n">
         <v>171</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>4395</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1846</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>5007</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>8630</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>12196</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n">
         <v>5008</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>372</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>903</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>746</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1467</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>6766</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>355</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>535</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>424</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>266</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>498</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-167</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-518</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-473</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>-1351</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>-11276</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>4561</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>2364</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>5480</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>9981</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>23472</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>1004</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>522</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>1207</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>2197</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>4065</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>3558</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>1842</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>4273</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>7784</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>19408</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n">
         <v>863</v>
       </c>
     </row>
@@ -4838,900 +4981,900 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>832</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n">
         <v>24405</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>5011</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>4508</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>4778</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>5091</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>30466</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>5025</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>4516</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>4780</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>5091</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>31298</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>479</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1023</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>863</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>1356</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>34998</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>37503</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>45718</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>6430</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>63832</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>4707</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>8703</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>992</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1962</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>2307</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>2616</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>1971</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>3330</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>3158</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>4502</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>42323</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>48658</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>51066</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>12415</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>71997</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>27067</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>32631</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>31700</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>70914</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>15060</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>69389</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>81289</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>82766</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>83329</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>87057</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>74414</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>85805</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>87546</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>88420</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>118355</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n">
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n">
         <v>5008</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>15436</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>17279</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>21552</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>29336</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>43736</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>16036</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>17879</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>22152</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>29936</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>49344</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>25424</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>19239</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>19239</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>27824</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>21639</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>21639</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>16829</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>12019</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n">
         <v>4810</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>4810</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>4810</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>4810</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>5345</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>6314</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>7327</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>3208</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>2835</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>8530</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>7965</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>8460</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>4082</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>20833</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>965</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>509</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>1197</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>2187</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>4011</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>4002</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>3132</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>3046</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>832</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>896</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>11699</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>23534</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>18861</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>26508</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="17" t="n">
         <v>23572</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>30554</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>46288</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>43756</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>41655</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>56957</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>58378</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>67927</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>65395</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>58484</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="17" t="n">
         <v>68976</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>74414</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>85805</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>87546</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>88420</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>118355</v>
       </c>
     </row>
@@ -5741,6 +5884,116 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>-22807</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>6694</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>-877</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>10045</v>
+      </c>
+      <c r="F2" s="17" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>25357</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-548</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>30095</v>
+      </c>
+      <c r="F4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
